--- a/output/Tables/2019/Resampling/1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>8534.388348745983</v>
+        <v>5334.649443884064</v>
       </c>
       <c r="B2">
-        <v>14250.36985719113</v>
+        <v>7937.357305739039</v>
       </c>
       <c r="C2">
-        <v>51484.92341172392</v>
+        <v>17242.27181308564</v>
       </c>
       <c r="D2">
-        <v>6.102087669353383</v>
+        <v>3.814274352377115</v>
       </c>
       <c r="E2">
-        <v>10.18901444789167</v>
+        <v>5.675210473603427</v>
       </c>
       <c r="F2">
-        <v>36.81172023938264</v>
+        <v>12.32822434635627</v>
       </c>
       <c r="G2">
-        <v>76.2760958669173</v>
+        <v>47.67842940471395</v>
       </c>
       <c r="H2">
-        <v>127.3626805986459</v>
+        <v>70.94013092004285</v>
       </c>
       <c r="I2">
-        <v>460.146502992283</v>
+        <v>154.1028043294533</v>
       </c>
       <c r="J2">
         <v>1</v>

--- a/output/Tables/2019/Resampling/1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>5334.649443884064</v>
+        <v>5447.94250677424</v>
       </c>
       <c r="B2">
-        <v>7937.357305739039</v>
+        <v>8069.682405845962</v>
       </c>
       <c r="C2">
-        <v>17242.27181308564</v>
+        <v>17253.78986805047</v>
       </c>
       <c r="D2">
-        <v>3.814274352377115</v>
+        <v>3.895278892343591</v>
       </c>
       <c r="E2">
-        <v>5.675210473603427</v>
+        <v>5.769822920179878</v>
       </c>
       <c r="F2">
-        <v>12.32822434635627</v>
+        <v>12.33645975565612</v>
       </c>
       <c r="G2">
-        <v>47.67842940471395</v>
+        <v>48.69098615429489</v>
       </c>
       <c r="H2">
-        <v>70.94013092004285</v>
+        <v>72.12278650224847</v>
       </c>
       <c r="I2">
-        <v>154.1028043294533</v>
+        <v>154.2057469457015</v>
       </c>
       <c r="J2">
         <v>1</v>
